--- a/16_Crypto_Digital_Assets/_template_CRYPTO.xlsx
+++ b/16_Crypto_Digital_Assets/_template_CRYPTO.xlsx
@@ -12,9 +12,12 @@
     <sheet name="Tokenomics" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Valuation" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Staking Yield" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Comparable Protocols" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Supply Emission Schedule" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="RefreshLog" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Perp Funding &amp; Basis" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Comparable Protocols" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Supply Emission Schedule" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Sources" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Checks" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="RefreshLog" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="133">
   <si>
     <t xml:space="preserve">[TOKEN] — Crypto / Digital Asset Model</t>
   </si>
@@ -172,6 +175,81 @@
     <t xml:space="preserve">Negative = staking rewards are pure dilution, not real cash flow</t>
   </si>
   <si>
+    <t xml:space="preserve">Perpetual Funding Rate &amp; Cash-and-Carry Basis Trade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A perp has no expiry, so it stays anchored to spot via a periodic funding payment instead: when the perp trades above spot (positive premium), longs pay shorts. A cash-and-carry basis trade -- long spot, short an equal notional of perp -- is delta-neutral to the underlying's price and collects that funding as its return, with basis-widening (not price) as the real risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perpetual futures price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spot / index price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding interval (hours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis trade notional ($, long spot / short perp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium (Perp - Spot) / Spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding rate this interval (simplified: = premium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real venues add a small clamped interest-rate component; this simplifies to the pure premium, which dominates in practice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding periods per year (365d x 24h / interval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annualized funding rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis Trade (long spot, short perp -- delta-neutral)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding received this interval (short perp collects when funding &gt; 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annualized funding income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spot/perp move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spot leg P&amp;L (long)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perp leg P&amp;L (short, tracks spot 1:1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net position P&amp;L (delta-neutral check)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The basis trade's return is the funding income above, isolated from price risk -- the net row is ~0 across every move because the position is deliberately delta-neutral. Real risk: the premium narrowing/widening before the trade is unwound, and exchange/counterparty risk on both legs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Comparable Protocols</t>
   </si>
   <si>
@@ -236,6 +314,102 @@
   </si>
   <si>
     <t xml:space="preserve">A holder who doesn't add to their position loses this much ownership share to new issuance over time -- the price needs to grow faster than dilution just to keep the position's dollar value from falling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding rate simplified to = premium, (Perp-Spot)/Spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common simplified perpetual-futures funding model used by major venues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real venues add a small clamped interest-rate component this omits; premium dominates in practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVT ratio, Mkt cap/TVL, FDV/TVL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard on-chain valuation multiples (crypto-native analogues to P/E, P/B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No universally agreed 'correct' NVT level -- used relatively (vs. history or comps), not as an absolute valuation anchor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat annual emission schedule (Supply Emission Schedule tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplified planning approximation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real token unlocks are usually cliff + linear per allocation bucket -- this is not a substitute for the actual unlock table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflationary yield vs. real yield split (Staking Yield tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard DeFi staking-yield decomposition (emissions dilution vs. protocol fee revenue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real yield requires accurate protocol fee-revenue data, which varies widely in disclosure quality across protocols</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis trade is delta-neutral: net P&amp;L is 0 across every spot/perp move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) -- long spot + short perp cancels price risk by construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annualized funding income = notional x annualized funding rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) once spot price is populated; "-" on a blank template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allocation percentages sum to 100% of max supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% (once allocations are populated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circulating supply never exceeds max supply in the emission schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -260,13 +434,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="168" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0\x"/>
+    <numFmt numFmtId="170" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="171" formatCode="General"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -418,7 +594,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -511,6 +687,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -524,6 +712,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -848,6 +1048,124 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:F14"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1257,13 +1575,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:I11"/>
+  <dimension ref="B2:G26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1271,238 +1589,213 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="5" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="C8" s="19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="C9" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="5" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="C12" s="23" t="str">
+        <f aca="false">IFERROR((C6-C7)/C7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="C13" s="24" t="str">
+        <f aca="false">C12</f>
+        <v>-</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="23" t="n">
-        <f aca="false">Valuation!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="23" t="n">
-        <f aca="false">Valuation!C12</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <f aca="false">Valuation!C6</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <f aca="false">Valuation!C8</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="str">
-        <f aca="false">IFERROR(C5/E5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H5" s="17" t="str">
-        <f aca="false">IFERROR(D5/E5,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I5" s="17" t="str">
-        <f aca="false">IFERROR(C5/(F5*365),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="17" t="str">
-        <f aca="false">IFERROR(C6/E6,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H6" s="17" t="str">
-        <f aca="false">IFERROR(D6/E6,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I6" s="17" t="str">
-        <f aca="false">IFERROR(C6/(F6*365),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="17" t="str">
-        <f aca="false">IFERROR(C7/E7,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H7" s="17" t="str">
-        <f aca="false">IFERROR(D7/E7,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I7" s="17" t="str">
-        <f aca="false">IFERROR(C7/(F7*365),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="17" t="str">
-        <f aca="false">IFERROR(C8/E8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H8" s="17" t="str">
-        <f aca="false">IFERROR(D8/E8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I8" s="17" t="str">
-        <f aca="false">IFERROR(C8/(F8*365),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="17" t="str">
-        <f aca="false">IFERROR(C9/E9,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H9" s="17" t="str">
-        <f aca="false">IFERROR(D9/E9,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I9" s="17" t="str">
-        <f aca="false">IFERROR(C9/(F9*365),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="17" t="str">
-        <f aca="false">IFERROR(C10/E10,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H10" s="17" t="str">
-        <f aca="false">IFERROR(D10/E10,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I10" s="17" t="str">
-        <f aca="false">IFERROR(C10/(F10*365),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="17" t="str">
-        <f aca="false">IFERROR(C11/E11,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H11" s="17" t="str">
-        <f aca="false">IFERROR(D11/E11,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I11" s="17" t="str">
-        <f aca="false">IFERROR(C11/(F11*365),"-")</f>
-        <v>-</v>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <f aca="false">IFERROR(365*24/C8,"-")</f>
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="22" t="str">
+        <f aca="false">IFERROR(C13*C14,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="16" t="str">
+        <f aca="false">IFERROR(C9*C13,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="25" t="str">
+        <f aca="false">IFERROR(C9*C15,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <f aca="false">$C$9*-0.2</f>
+        <v>-0</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <f aca="false">$C$9*-0.1</f>
+        <v>-0</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <f aca="false">$C$9*0</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <f aca="false">$C$9*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <f aca="false">$C$9*0.2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <f aca="false">-$C$9*-0.2</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <f aca="false">-$C$9*-0.1</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <f aca="false">-$C$9*0</f>
+        <v>-0</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <f aca="false">-$C$9*0.1</f>
+        <v>-0</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <f aca="false">-$C$9*0.2</f>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <f aca="false">C22+C23</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <f aca="false">D22+D23</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <f aca="false">E22+E23</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <f aca="false">F22+F23</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <f aca="false">G22+G23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1521,126 +1814,252 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G10"/>
+  <dimension ref="A2:I11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>60</v>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="26" t="n">
+        <f aca="false">Valuation!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <f aca="false">Valuation!C12</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <f aca="false">Valuation!C6</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <f aca="false">Valuation!C8</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="17" t="str">
+        <f aca="false">IFERROR(C5/E5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H5" s="17" t="str">
+        <f aca="false">IFERROR(D5/E5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I5" s="17" t="str">
+        <f aca="false">IFERROR(C5/(F5*365),"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>65</v>
+      <c r="B6" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17" t="str">
+        <f aca="false">IFERROR(C6/E6,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H6" s="17" t="str">
+        <f aca="false">IFERROR(D6/E6,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I6" s="17" t="str">
+        <f aca="false">IFERROR(C6/(F6*365),"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="26" t="n">
-        <f aca="false">Tokenomics!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="20" t="n">
-        <f aca="false">MIN(Tokenomics!$C$10,C7+Tokenomics!$C$10*$C$4)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="20" t="n">
-        <f aca="false">MIN(Tokenomics!$C$10,D7+Tokenomics!$C$10*$C$4)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="20" t="n">
-        <f aca="false">MIN(Tokenomics!$C$10,E7+Tokenomics!$C$10*$C$4)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <f aca="false">MIN(Tokenomics!$C$10,F7+Tokenomics!$C$10*$C$4)</f>
-        <v>0</v>
+      <c r="B7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17" t="str">
+        <f aca="false">IFERROR(C7/E7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H7" s="17" t="str">
+        <f aca="false">IFERROR(D7/E7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I7" s="17" t="str">
+        <f aca="false">IFERROR(C7/(F7*365),"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="21" t="str">
-        <f aca="false">IFERROR(1-$C$7/C7,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D8" s="21" t="str">
-        <f aca="false">IFERROR(1-$C$7/D7,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E8" s="21" t="str">
-        <f aca="false">IFERROR(1-$C$7/E7,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F8" s="21" t="str">
-        <f aca="false">IFERROR(1-$C$7/F7,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G8" s="21" t="str">
-        <f aca="false">IFERROR(1-$C$7/G7,"-")</f>
+      <c r="B8" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="17" t="str">
+        <f aca="false">IFERROR(C8/E8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H8" s="17" t="str">
+        <f aca="false">IFERROR(D8/E8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I8" s="17" t="str">
+        <f aca="false">IFERROR(C8/(F8*365),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">Valuation!$C$5*C7</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <f aca="false">Valuation!$C$5*D7</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <f aca="false">Valuation!$C$5*E7</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <f aca="false">Valuation!$C$5*F7</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <f aca="false">Valuation!$C$5*G7</f>
-        <v>0</v>
+      <c r="B9" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17" t="str">
+        <f aca="false">IFERROR(C9/E9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H9" s="17" t="str">
+        <f aca="false">IFERROR(D9/E9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I9" s="17" t="str">
+        <f aca="false">IFERROR(C9/(F9*365),"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
-        <v>69</v>
+      <c r="B10" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="str">
+        <f aca="false">IFERROR(C10/E10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H10" s="17" t="str">
+        <f aca="false">IFERROR(D10/E10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I10" s="17" t="str">
+        <f aca="false">IFERROR(C10/(F10*365),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="17" t="str">
+        <f aca="false">IFERROR(C11/E11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H11" s="17" t="str">
+        <f aca="false">IFERROR(D11/E11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I11" s="17" t="str">
+        <f aca="false">IFERROR(C11/(F11*365),"-")</f>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
@@ -1659,107 +2078,327 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F14"/>
+  <dimension ref="B2:G10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>75</v>
+      <c r="B4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <f aca="false">Tokenomics!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <f aca="false">MIN(Tokenomics!$C$10,C7+Tokenomics!$C$10*$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <f aca="false">MIN(Tokenomics!$C$10,D7+Tokenomics!$C$10*$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <f aca="false">MIN(Tokenomics!$C$10,E7+Tokenomics!$C$10*$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <f aca="false">MIN(Tokenomics!$C$10,F7+Tokenomics!$C$10*$C$4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/C7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/D7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/E7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/F7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/G7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*C7</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*D7</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*E7</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*F7</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+      <c r="B5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
+      <c r="B6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
+      <c r="B7" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
+      <c r="B8" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
+      <c r="B9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="32" t="n">
+        <f aca="false">SUMPRODUCT(ABS('Perp Funding &amp; Basis'!C24:G24))</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="32" t="str">
+        <f aca="false">IFERROR('Perp Funding &amp; Basis'!C19-('Perp Funding &amp; Basis'!C9*'Perp Funding &amp; Basis'!C15),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="32" t="n">
+        <f aca="false">SUM(Tokenomics!D5:D9)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="32" t="b">
+        <f aca="false">IF(MAX('Supply Emission Schedule'!C7:G7)&lt;=Tokenomics!C10,TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>126</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
